--- a/Excel_Reports/Load_Performance_Test_Report.xlsx
+++ b/Excel_Reports/Load_Performance_Test_Report.xlsx
@@ -1995,7 +1995,7 @@
     <t>Execution Start Time</t>
   </si>
   <si>
-    <t>20/8/2026, 1:35:48 pm</t>
+    <t>20/8/2026, 1:49:49 pm</t>
   </si>
   <si>
     <t>Total Unique Load Scenarios</t>
